--- a/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_FULL_9_winter.xlsx
+++ b/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_FULL_9_winter.xlsx
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -414,316 +414,350 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>39400</v>
+        <v>38678</v>
       </c>
       <c r="B2">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="D2">
-        <v>2008</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>39765</v>
+        <v>39044</v>
       </c>
       <c r="B3">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="D3">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="E3">
-        <v>-0.1475798440394471</v>
+        <v>1.485471308700004</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>40130</v>
+        <v>39408</v>
       </c>
       <c r="B4">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="C4">
-        <v>0.348613976222456</v>
+        <v>1.754772933362747</v>
       </c>
       <c r="D4">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="E4">
-        <v>-0.01626791011750672</v>
+        <v>1.319969052049697</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>40494</v>
+        <v>39777</v>
       </c>
       <c r="B5">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C5">
-        <v>-0.1384957661262676</v>
+        <v>2.213924989827909</v>
       </c>
       <c r="D5">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="E5">
-        <v>0.8386661657977079</v>
+        <v>2.35021944732241</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>40862</v>
+        <v>40141</v>
       </c>
       <c r="B6">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="C6">
-        <v>1.566479473280191</v>
+        <v>2.534145137403332</v>
       </c>
       <c r="D6">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E6">
-        <v>0.7522429756626314</v>
+        <v>1.707775012144053</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>41228</v>
+        <v>40505</v>
       </c>
       <c r="B7">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C7">
-        <v>0.7307568962937161</v>
+        <v>2.088987206093629</v>
       </c>
       <c r="D7">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="E7">
-        <v>0.625650411734191</v>
+        <v>1.815484941493861</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>41592</v>
+        <v>40871</v>
       </c>
       <c r="B8">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C8">
-        <v>0.8188188121642126</v>
+        <v>1.212532518945841</v>
       </c>
       <c r="D8">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="E8">
-        <v>0.8799027686248406</v>
+        <v>1.823050067264487</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>41957</v>
+        <v>41236</v>
       </c>
       <c r="B9">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C9">
-        <v>0.9180054319587239</v>
+        <v>1.196784623675229</v>
       </c>
       <c r="D9">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="E9">
-        <v>1.191577176688963</v>
+        <v>1.272951221568497</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>42321</v>
+        <v>41600</v>
       </c>
       <c r="B10">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C10">
-        <v>1.9846842782967</v>
+        <v>0.4723812919182446</v>
       </c>
       <c r="D10">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="E10">
-        <v>1.088188976309357</v>
+        <v>1.245309094294522</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>42689</v>
+        <v>41968</v>
       </c>
       <c r="B11">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C11">
-        <v>1.755995812646982</v>
+        <v>0.8777276606119377</v>
       </c>
       <c r="D11">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="E11">
-        <v>1.107792786355444</v>
+        <v>1.781555391251755</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>43053</v>
+        <v>42332</v>
       </c>
       <c r="B12">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C12">
-        <v>1.946965557828384</v>
+        <v>2.290662253244125</v>
       </c>
       <c r="D12">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="E12">
-        <v>1.192420150523787</v>
+        <v>2.449235417553597</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>43418</v>
+        <v>42698</v>
       </c>
       <c r="B13">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C13">
-        <v>1.064321453542272</v>
+        <v>4.109910756223556</v>
       </c>
       <c r="D13">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="E13">
-        <v>0.6327208244686799</v>
+        <v>2.713490631531856</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>43783</v>
+        <v>43062</v>
       </c>
       <c r="B14">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C14">
-        <v>1.361817904277718</v>
+        <v>1.660180415270074</v>
       </c>
       <c r="D14">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="E14">
-        <v>1.18054321292711</v>
+        <v>1.208622698681161</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>44159</v>
+        <v>43427</v>
       </c>
       <c r="B15">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C15">
-        <v>-4.352425014431327</v>
+        <v>1.0578868654878</v>
       </c>
       <c r="D15">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="E15">
-        <v>1.562935589653547</v>
+        <v>1.533790036386806</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>44525</v>
+        <v>43791</v>
       </c>
       <c r="B16">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C16">
-        <v>-1.761645650979182</v>
+        <v>1.727536231884064</v>
       </c>
       <c r="D16">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="E16">
-        <v>5.632867463658853</v>
+        <v>2.237075695376634</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>44890</v>
+        <v>44159</v>
       </c>
       <c r="B17">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C17">
-        <v>5.20787683103745</v>
+        <v>3.806466406787412</v>
       </c>
       <c r="D17">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E17">
-        <v>2.033577491950478</v>
+        <v>3.165947654822987</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>45254</v>
+        <v>44525</v>
       </c>
       <c r="B18">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C18">
-        <v>-0.9008525709169657</v>
+        <v>3.70707249977813</v>
       </c>
       <c r="D18">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E18">
-        <v>0.1302881545538925</v>
+        <v>1.583310261728132</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>45618</v>
+        <v>44890</v>
       </c>
       <c r="B19">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C19">
-        <v>0.2738544794132602</v>
+        <v>1.717176010541088</v>
       </c>
       <c r="D19">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E19">
-        <v>0.4325397337088255</v>
+        <v>1.672885884596687</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
+        <v>45254</v>
+      </c>
+      <c r="B20">
+        <v>2023</v>
+      </c>
+      <c r="C20">
+        <v>-1.789118639096632</v>
+      </c>
+      <c r="D20">
+        <v>2024</v>
+      </c>
+      <c r="E20">
+        <v>0.7888472770010146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2">
+        <v>45618</v>
+      </c>
+      <c r="B21">
+        <v>2024</v>
+      </c>
+      <c r="C21">
+        <v>2.251694235954238</v>
+      </c>
+      <c r="D21">
+        <v>2025</v>
+      </c>
+      <c r="E21">
+        <v>2.403558697526265</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2">
         <v>45986</v>
       </c>
-      <c r="B20">
+      <c r="B22">
         <v>2025</v>
       </c>
-      <c r="C20">
-        <v>0.8976398032236155</v>
-      </c>
-      <c r="D20">
+      <c r="C22">
+        <v>2.593796720377783</v>
+      </c>
+      <c r="D22">
         <v>2026</v>
       </c>
-      <c r="E20">
-        <v>0.4761827721654566</v>
+      <c r="E22">
+        <v>2.079815056622447</v>
       </c>
     </row>
   </sheetData>
